--- a/data/trans_orig/IP2004-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP2004-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42183</t>
+          <t>42303</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94972</t>
+          <t>94990</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17623</t>
+          <t>18140</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20751</t>
+          <t>20245</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19135</t>
+          <t>18326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34026</t>
+          <t>34518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77195</t>
+          <t>76678</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87386</t>
+          <t>87518</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84092</t>
+          <t>84598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95844</t>
+          <t>95854</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>165635</t>
+          <t>165143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180526</t>
+          <t>181335</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2391</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60580</t>
+          <t>60150</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64177</t>
+          <t>63929</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126497</t>
+          <t>126331</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65326</t>
+          <t>65502</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142333</t>
+          <t>141934</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6766</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34299</t>
+          <t>34930</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39260</t>
+          <t>39904</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39387</t>
+          <t>39373</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75903</t>
+          <t>75877</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>81973</t>
+          <t>81938</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50235</t>
+          <t>49716</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53413</t>
+          <t>52233</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105203</t>
+          <t>104652</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>121504</t>
+          <t>122133</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>244649</t>
+          <t>244572</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9074</t>
+          <t>8238</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>13286</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>141801</t>
+          <t>142637</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>149423</t>
+          <t>149440</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>146063</t>
+          <t>146867</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>152547</t>
+          <t>152283</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>291673</t>
+          <t>291514</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>300698</t>
+          <t>300472</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>15021</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30106</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15049</t>
+          <t>15282</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29460</t>
+          <t>29798</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>34325</t>
+          <t>34895</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>54994</t>
+          <t>55184</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>612709</t>
+          <t>613056</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>627687</t>
+          <t>628141</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>651244</t>
+          <t>650906</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>665655</t>
+          <t>665422</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1268872</t>
+          <t>1268682</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1289541</t>
+          <t>1288971</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>504</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11649</t>
+          <t>12086</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14925</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48344</t>
+          <t>48417</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53933</t>
+          <t>53939</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48507</t>
+          <t>48070</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57058</t>
+          <t>56812</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99674</t>
+          <t>99068</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109614</t>
+          <t>109735</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6697</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>6960</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9708</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89467</t>
+          <t>89277</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95316</t>
+          <t>95325</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93930</t>
+          <t>93689</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>186916</t>
+          <t>187461</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>195039</t>
+          <t>195338</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -4742,39 +4742,39 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6762</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,88%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6482</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>920</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55644</t>
+          <t>55364</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61475</t>
+          <t>61467</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62516</t>
+          <t>62979</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121483</t>
+          <t>121016</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127627</t>
+          <t>127626</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>827</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>7628</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67133</t>
+          <t>66512</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72885</t>
+          <t>72728</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75003</t>
+          <t>74958</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>144261</t>
+          <t>144732</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151055</t>
+          <t>151044</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>7920</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13747</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33029</t>
+          <t>33420</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40355</t>
+          <t>40388</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38187</t>
+          <t>37323</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43888</t>
+          <t>43891</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73353</t>
+          <t>73429</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82806</t>
+          <t>82605</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9403</t>
+          <t>9359</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>11634</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118137</t>
+          <t>118181</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>125533</t>
+          <t>125697</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>125225</t>
+          <t>124868</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>246723</t>
+          <t>246481</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>255372</t>
+          <t>255374</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9097</t>
+          <t>9021</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>151272</t>
+          <t>151470</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>156983</t>
+          <t>156994</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>159345</t>
+          <t>159522</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>164060</t>
+          <t>164058</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>313233</t>
+          <t>313309</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>320390</t>
+          <t>320404</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13929</t>
+          <t>14564</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>29559</t>
+          <t>29592</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>10646</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>25767</t>
+          <t>25644</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>28013</t>
+          <t>28308</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>48995</t>
+          <t>49648</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>632658</t>
+          <t>632625</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>648288</t>
+          <t>647653</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>676389</t>
+          <t>676512</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>691303</t>
+          <t>691510</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1315377</t>
+          <t>1314724</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1336359</t>
+          <t>1336064</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12210</t>
+          <t>11969</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46229</t>
+          <t>46963</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53766</t>
+          <t>53750</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53624</t>
+          <t>53146</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59918</t>
+          <t>60374</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104360</t>
+          <t>104601</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112799</t>
+          <t>113397</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>698</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>710</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95070</t>
+          <t>94352</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>101206</t>
+          <t>101305</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106381</t>
+          <t>106386</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>198454</t>
+          <t>198381</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>204721</t>
+          <t>204709</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>817</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>833</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54574</t>
+          <t>53896</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60306</t>
+          <t>60305</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62037</t>
+          <t>63046</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>119123</t>
+          <t>119367</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126236</t>
+          <t>126234</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13606</t>
+          <t>12336</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>18512</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59156</t>
+          <t>60426</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68894</t>
+          <t>69245</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69810</t>
+          <t>69943</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76401</t>
+          <t>76396</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132447</t>
+          <t>132012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>144121</t>
+          <t>144129</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38842</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>79866</t>
+          <t>80799</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45927</t>
+          <t>46604</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49935</t>
+          <t>49982</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99221</t>
+          <t>99181</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>104404</t>
+          <t>104418</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>597</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>712</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124299</t>
+          <t>124201</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>129229</t>
+          <t>129240</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>130378</t>
+          <t>130311</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>257075</t>
+          <t>256855</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>262922</t>
+          <t>262920</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>146295</t>
+          <t>146258</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>305088</t>
+          <t>305094</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26752</t>
+          <t>27149</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17323</t>
+          <t>17999</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>21945</t>
+          <t>22538</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>40238</t>
+          <t>40371</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>631885</t>
+          <t>631488</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>646158</t>
+          <t>646063</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>683572</t>
+          <t>682896</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>694288</t>
+          <t>694113</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1319294</t>
+          <t>1319161</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1337587</t>
+          <t>1336994</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73921</t>
+          <t>73559</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>146899</t>
+          <t>146822</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2519</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>342</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>123356</t>
+          <t>123048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>122233</t>
+          <t>122149</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>246755</t>
+          <t>247002</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>249963</t>
+          <t>249937</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53370</t>
+          <t>53786</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56859</t>
+          <t>57234</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64694</t>
+          <t>64397</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112421</t>
+          <t>113019</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>121040</t>
+          <t>121064</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>7679</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>903</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9294</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63110</t>
+          <t>62670</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68559</t>
+          <t>67688</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>135310</t>
+          <t>135809</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>143536</t>
+          <t>143701</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31379</t>
+          <t>31260</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37429</t>
+          <t>37705</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71399</t>
+          <t>71044</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1692</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9176</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15014</t>
+          <t>14435</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20473</t>
+          <t>20341</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>114403</t>
+          <t>114094</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>121978</t>
+          <t>121887</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>139843</t>
+          <t>140422</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>150590</t>
+          <t>150839</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>257962</t>
+          <t>258094</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>271148</t>
+          <t>270851</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>5713</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>148803</t>
+          <t>149217</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>278439</t>
+          <t>279289</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14928</t>
+          <t>13380</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13466,42 +13466,42 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>17057</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>10765</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>25750</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
           <t>2,28%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>17057</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>10934</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>26191</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17140</t>
+          <t>16155</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>34804</t>
+          <t>35730</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>641143</t>
+          <t>642691</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>652100</t>
+          <t>652064</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,47 +13574,47 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>97,96%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>730408</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>721715</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>736700</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
           <t>97,72%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>730408</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>721274</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>736531</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>97,72%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1368732</t>
+          <t>1367806</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1386396</t>
+          <t>1387381</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
